--- a/Avaliacao360/C2/Avaliacao_360_PI-IV_2026-2_C2_Lucas.xlsx
+++ b/Avaliacao360/C2/Avaliacao_360_PI-IV_2026-2_C2_Lucas.xlsx
@@ -1269,7 +1269,7 @@
         <v/>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="13" t="n">
         <v>6</v>
